--- a/carsystem/Alpine_Estimate_Data_20260624.xlsx
+++ b/carsystem/Alpine_Estimate_Data_20260624.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3044f8daa6472af6/Desktop/알파인홈페이지 이미지/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\안티그래피티 work\alpinehompage\carsystem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{EA0CA4F3-B11F-4BE7-96BD-5412542B5BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{679FEDF4-0323-496F-95A8-AF22F643387F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{477181B5-1E14-4C08-A6F5-12D72E3F8595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28305" yWindow="480" windowWidth="28920" windowHeight="14745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27780" yWindow="150" windowWidth="26790" windowHeight="14745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EstimateData" sheetId="1" r:id="rId1"/>
@@ -12383,17 +12383,17 @@
       <c r="Z125" t="s">
         <v>432</v>
       </c>
+      <c r="AA125" t="s">
+        <v>409</v>
+      </c>
+      <c r="AB125" t="s">
+        <v>410</v>
+      </c>
       <c r="AE125" t="s">
         <v>433</v>
       </c>
       <c r="AF125" t="s">
         <v>434</v>
-      </c>
-      <c r="AM125" t="s">
-        <v>409</v>
-      </c>
-      <c r="AN125" t="s">
-        <v>410</v>
       </c>
       <c r="AO125" t="s">
         <v>411</v>
